--- a/Digitised_Records_2026_03_13.xlsx
+++ b/Digitised_Records_2026_03_13.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sotonac-my.sharepoint.com/personal/ck1g20_soton_ac_uk/Documents/Documents/PhD/20_Historical_record_catalogue/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="433" documentId="8_{22737A28-F927-43B1-8C9E-30BC7D7DE0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B91F41DE-D69E-42C0-9AAF-D1BADBDE9B12}"/>
+  <xr:revisionPtr revIDLastSave="442" documentId="8_{22737A28-F927-43B1-8C9E-30BC7D7DE0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31460A7D-EDF8-4373-82AC-3ED495FFA5CD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8FB86131-9B33-41BE-BB40-45738662AB11}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3755" uniqueCount="757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3755" uniqueCount="756">
   <si>
     <t>Study</t>
   </si>
@@ -1102,9 +1102,6 @@
     <t>Tide gauge 1 (Belfast)</t>
   </si>
   <si>
-    <t>UnGraph (Digitisation software)</t>
-  </si>
-  <si>
     <t>Continuous</t>
   </si>
   <si>
@@ -1534,9 +1531,6 @@
     <t>Poole Bridge</t>
   </si>
   <si>
-    <t>Specalised Algorthim</t>
-  </si>
-  <si>
     <t>Continuous, weekly max</t>
   </si>
   <si>
@@ -1666,18 +1660,12 @@
     <t>Williamstown</t>
   </si>
   <si>
-    <t>plotdigitiser (Digitisation Software)</t>
-  </si>
-  <si>
     <t>Digitizing the Williamstown, Australia Tide‐Gauge Record Back to 1872: Insights Into Changing Extremes - McInnes - 2024 - Journal of Geophysical Research: Oceans - Wiley Online Library</t>
   </si>
   <si>
     <t>Dún Laoghaire Harbour</t>
   </si>
   <si>
-    <t>WebPlotDigitiser (Digitisation software)</t>
-  </si>
-  <si>
     <t>The accurate digitization of historical sea level records - McLoughlin - 2024 - Geoscience Data Journal - Wiley Online Library</t>
   </si>
   <si>
@@ -2369,6 +2357,15 @@
   </si>
   <si>
     <t>Kenwright, TBP</t>
+  </si>
+  <si>
+    <t>Plot Digitizer</t>
+  </si>
+  <si>
+    <t>WebPlotDigitiser</t>
+  </si>
+  <si>
+    <t>UnGraph</t>
   </si>
 </sst>
 </file>
@@ -3047,13 +3044,13 @@
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>8</v>
@@ -3062,7 +3059,7 @@
         <v>9</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>11</v>
@@ -3070,7 +3067,7 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>12</v>
@@ -3115,7 +3112,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>18</v>
@@ -3147,7 +3144,7 @@
         <v>136.16666666666666</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>10</v>
@@ -3161,7 +3158,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>23</v>
@@ -3193,7 +3190,7 @@
         <v>137.13636363636363</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>10</v>
@@ -3207,7 +3204,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>25</v>
@@ -3239,7 +3236,7 @@
         <v>135.66666666666666</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>10</v>
@@ -3278,7 +3275,7 @@
         <v>147</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="J6" s="5">
         <v>0</v>
@@ -3298,7 +3295,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>33</v>
@@ -3323,13 +3320,13 @@
         <v>58.6</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="J7" s="5">
         <v>0.4</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>10</v>
@@ -3343,7 +3340,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>36</v>
@@ -3368,13 +3365,13 @@
         <v>24.3</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="J8" s="5">
         <v>0.7</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>10</v>
@@ -3388,7 +3385,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>37</v>
@@ -3413,13 +3410,13 @@
         <v>67.900000000000006</v>
       </c>
       <c r="I9" s="42" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="J9" s="5">
         <v>0.1</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>10</v>
@@ -3433,7 +3430,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>38</v>
@@ -3458,13 +3455,13 @@
         <v>11.7</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="J10" s="5">
         <v>0.3</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>10</v>
@@ -3478,7 +3475,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>39</v>
@@ -3509,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>10</v>
@@ -3523,7 +3520,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>40</v>
@@ -3548,13 +3545,13 @@
         <v>21.7</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="J12" s="5">
         <v>0.3</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>10</v>
@@ -3568,7 +3565,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>41</v>
@@ -3593,13 +3590,13 @@
         <v>15.3</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="J13" s="5">
         <v>0.7</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>10</v>
@@ -3613,7 +3610,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>42</v>
@@ -3644,7 +3641,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>10</v>
@@ -3658,7 +3655,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>43</v>
@@ -3689,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>10</v>
@@ -3703,7 +3700,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>46</v>
@@ -3734,7 +3731,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>10</v>
@@ -3748,7 +3745,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>47</v>
@@ -3779,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>10</v>
@@ -3793,7 +3790,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>48</v>
@@ -3824,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>10</v>
@@ -3838,7 +3835,7 @@
     </row>
     <row r="19" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>49</v>
@@ -3885,7 +3882,7 @@
     </row>
     <row r="20" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>49</v>
@@ -3919,7 +3916,7 @@
         <v>44</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>10</v>
@@ -3933,7 +3930,7 @@
     </row>
     <row r="21" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B21" t="s">
         <v>53</v>
@@ -3978,7 +3975,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>54</v>
@@ -4003,14 +4000,14 @@
         <v>211</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="J22" s="5">
         <f>7+9</f>
         <v>16</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>10</v>
@@ -4024,7 +4021,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>57</v>
@@ -4056,7 +4053,7 @@
         <v>124</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>10</v>
@@ -4101,7 +4098,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>10</v>
@@ -4146,7 +4143,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>10</v>
@@ -4191,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>10</v>
@@ -4237,7 +4234,7 @@
         <v>14</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>10</v>
@@ -4282,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>10</v>
@@ -4327,7 +4324,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>10</v>
@@ -4372,7 +4369,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>10</v>
@@ -4417,7 +4414,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>10</v>
@@ -4462,7 +4459,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>10</v>
@@ -4507,7 +4504,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>10</v>
@@ -4552,7 +4549,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>10</v>
@@ -4597,7 +4594,7 @@
         <v>0</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>10</v>
@@ -4642,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L36" s="3" t="s">
         <v>10</v>
@@ -4687,7 +4684,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L37" s="3" t="s">
         <v>10</v>
@@ -4732,7 +4729,7 @@
         <v>0</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L38" s="3" t="s">
         <v>10</v>
@@ -4777,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>10</v>
@@ -4822,7 +4819,7 @@
         <v>0</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L40" s="3" t="s">
         <v>10</v>
@@ -4867,7 +4864,7 @@
         <v>0</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>10</v>
@@ -4912,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>10</v>
@@ -4957,7 +4954,7 @@
         <v>0</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>10</v>
@@ -5002,7 +4999,7 @@
         <v>0</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>10</v>
@@ -5047,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>10</v>
@@ -5092,7 +5089,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>10</v>
@@ -5137,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>10</v>
@@ -5182,7 +5179,7 @@
         <v>0</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>10</v>
@@ -5227,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>10</v>
@@ -5272,7 +5269,7 @@
         <v>0</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>10</v>
@@ -5317,7 +5314,7 @@
         <v>0</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>10</v>
@@ -5362,7 +5359,7 @@
         <v>0</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>10</v>
@@ -5407,7 +5404,7 @@
         <v>0</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L53" s="3" t="s">
         <v>10</v>
@@ -5452,7 +5449,7 @@
         <v>0</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>10</v>
@@ -5466,7 +5463,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>109</v>
@@ -5511,7 +5508,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>112</v>
@@ -5536,7 +5533,7 @@
         <v>103.5</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="J56" s="5">
         <v>0.5</v>
@@ -5556,7 +5553,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>113</v>
@@ -5587,7 +5584,7 @@
         <v>0</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>10</v>
@@ -5601,7 +5598,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>116</v>
@@ -5633,7 +5630,7 @@
         <v>0.97809719370294324</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>10</v>
@@ -5647,7 +5644,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>118</v>
@@ -5678,7 +5675,7 @@
         <v>18</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>10</v>
@@ -5692,7 +5689,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>121</v>
@@ -5724,7 +5721,7 @@
         <v>32</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>10</v>
@@ -5738,7 +5735,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>123</v>
@@ -5783,7 +5780,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>123</v>
@@ -5814,7 +5811,7 @@
         <v>0</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>10</v>
@@ -5828,7 +5825,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>125</v>
@@ -5860,7 +5857,7 @@
         <v>12.202600958247775</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L63" s="3" t="s">
         <v>10</v>
@@ -5874,7 +5871,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>125</v>
@@ -5920,7 +5917,7 @@
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>130</v>
@@ -5965,7 +5962,7 @@
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>132</v>
@@ -6381,7 +6378,7 @@
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A74" s="19" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>150</v>
@@ -6412,7 +6409,7 @@
         <v>1</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L74" s="3" t="s">
         <v>10</v>
@@ -6426,7 +6423,7 @@
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A75" s="19" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B75" s="12" t="s">
         <v>152</v>
@@ -6470,7 +6467,7 @@
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A76" s="19" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>155</v>
@@ -6514,7 +6511,7 @@
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A77" s="19" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>144</v>
@@ -6558,7 +6555,7 @@
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A78" s="19" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>140</v>
@@ -6602,7 +6599,7 @@
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A79" s="19" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B79" s="12" t="s">
         <v>156</v>
@@ -6646,7 +6643,7 @@
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A80" s="19" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>157</v>
@@ -6690,7 +6687,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" s="19" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="B81" s="12" t="s">
         <v>158</v>
@@ -6734,7 +6731,7 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B82" s="10" t="s">
         <v>160</v>
@@ -6765,7 +6762,7 @@
         <v>0</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L82" s="3" t="s">
         <v>10</v>
@@ -6779,7 +6776,7 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B83" s="10" t="s">
         <v>162</v>
@@ -6810,7 +6807,7 @@
         <v>1</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>10</v>
@@ -6821,7 +6818,7 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B84" s="10" t="s">
         <v>163</v>
@@ -6852,7 +6849,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L84" s="3" t="s">
         <v>10</v>
@@ -6863,7 +6860,7 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B85" s="10" t="s">
         <v>164</v>
@@ -6906,7 +6903,7 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B86" s="10" t="s">
         <v>166</v>
@@ -6937,7 +6934,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L86" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6945,7 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>167</v>
@@ -6979,7 +6976,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L87" s="3" t="s">
         <v>10</v>
@@ -6993,7 +6990,7 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>169</v>
@@ -7025,7 +7022,7 @@
         <v>0.39698836413415467</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L88" s="3" t="s">
         <v>10</v>
@@ -7039,7 +7036,7 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>172</v>
@@ -7085,7 +7082,7 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>175</v>
@@ -7116,7 +7113,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L90" s="3" t="s">
         <v>10</v>
@@ -7130,7 +7127,7 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>179</v>
@@ -7162,7 +7159,7 @@
         <v>0.91991786447638602</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>10</v>
@@ -7176,7 +7173,7 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>182</v>
@@ -7222,7 +7219,7 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>186</v>
@@ -7268,7 +7265,7 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>187</v>
@@ -7313,7 +7310,7 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>189</v>
@@ -7358,7 +7355,7 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>190</v>
@@ -7403,7 +7400,7 @@
     </row>
     <row r="97" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="43" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="B97" s="16" t="s">
         <v>191</v>
@@ -7448,7 +7445,7 @@
     </row>
     <row r="98" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="43" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="B98" s="16" t="s">
         <v>196</v>
@@ -7473,13 +7470,13 @@
         <v>30</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="J98" s="5">
         <v>39</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="L98" s="3" t="s">
         <v>10</v>
@@ -7493,7 +7490,7 @@
     </row>
     <row r="99" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="43" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="B99" s="16" t="s">
         <v>198</v>
@@ -7518,14 +7515,14 @@
         <v>24</v>
       </c>
       <c r="I99" s="10" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="J99" s="5">
         <f>48+22+14</f>
         <v>84</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="L99" s="3" t="s">
         <v>10</v>
@@ -7539,7 +7536,7 @@
     </row>
     <row r="100" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="43" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="B100" s="16" t="s">
         <v>199</v>
@@ -7571,7 +7568,7 @@
         <v>148</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>10</v>
@@ -7585,7 +7582,7 @@
     </row>
     <row r="101" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="43" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="B101" s="16" t="s">
         <v>201</v>
@@ -7616,7 +7613,7 @@
         <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>10</v>
@@ -7630,7 +7627,7 @@
     </row>
     <row r="102" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="43" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="B102" s="16" t="s">
         <v>202</v>
@@ -7661,7 +7658,7 @@
         <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>10</v>
@@ -7675,7 +7672,7 @@
     </row>
     <row r="103" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="43" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B103" s="16" t="s">
         <v>203</v>
@@ -7720,7 +7717,7 @@
     </row>
     <row r="104" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="43" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B104" s="16" t="s">
         <v>203</v>
@@ -7751,7 +7748,7 @@
         <v>0</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L104" s="3" t="s">
         <v>10</v>
@@ -7765,7 +7762,7 @@
     </row>
     <row r="105" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="43" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B105" s="16" t="s">
         <v>206</v>
@@ -7810,7 +7807,7 @@
     </row>
     <row r="106" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="43" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B106" s="16" t="s">
         <v>208</v>
@@ -7855,7 +7852,7 @@
     </row>
     <row r="107" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="43" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B107" s="16" t="s">
         <v>209</v>
@@ -7900,7 +7897,7 @@
     </row>
     <row r="108" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="43" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B108" s="16" t="s">
         <v>210</v>
@@ -7931,7 +7928,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L108" s="3" t="s">
         <v>30</v>
@@ -7945,7 +7942,7 @@
     </row>
     <row r="109" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="43" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B109" s="16" t="s">
         <v>211</v>
@@ -7970,13 +7967,13 @@
         <v>45</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="J109" s="5">
         <v>9</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L109" s="3" t="s">
         <v>30</v>
@@ -7990,7 +7987,7 @@
     </row>
     <row r="110" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="43" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B110" s="16" t="s">
         <v>212</v>
@@ -8035,7 +8032,7 @@
     </row>
     <row r="111" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="43" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B111" s="16" t="s">
         <v>213</v>
@@ -8080,7 +8077,7 @@
     </row>
     <row r="112" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="43" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B112" s="16" t="s">
         <v>214</v>
@@ -8125,7 +8122,7 @@
     </row>
     <row r="113" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="43" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B113" s="16" t="s">
         <v>216</v>
@@ -8170,7 +8167,7 @@
     </row>
     <row r="114" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="43" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B114" s="16" t="s">
         <v>217</v>
@@ -8215,7 +8212,7 @@
     </row>
     <row r="115" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="43" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B115" s="16" t="s">
         <v>218</v>
@@ -8240,7 +8237,7 @@
         <v>113</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="J115" s="5">
         <v>2</v>
@@ -8260,7 +8257,7 @@
     </row>
     <row r="116" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="43" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B116" s="16" t="s">
         <v>219</v>
@@ -8291,7 +8288,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L116" s="3" t="s">
         <v>30</v>
@@ -8305,7 +8302,7 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>220</v>
@@ -8330,7 +8327,7 @@
         <v>29</v>
       </c>
       <c r="I117" s="10" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="J117" s="5">
         <v>5</v>
@@ -8350,7 +8347,7 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>220</v>
@@ -8381,7 +8378,7 @@
         <v>0</v>
       </c>
       <c r="K118" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L118" s="3" t="s">
         <v>10</v>
@@ -8395,7 +8392,7 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>223</v>
@@ -8426,7 +8423,7 @@
         <v>0</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L119" s="3" t="s">
         <v>10</v>
@@ -8440,7 +8437,7 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>224</v>
@@ -8465,7 +8462,7 @@
         <v>17</v>
       </c>
       <c r="I120" s="10" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="J120" s="5">
         <f>4</f>
@@ -8486,7 +8483,7 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>225</v>
@@ -8517,7 +8514,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L121" s="3" t="s">
         <v>10</v>
@@ -8531,7 +8528,7 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>226</v>
@@ -8562,7 +8559,7 @@
         <v>0</v>
       </c>
       <c r="K122" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L122" s="3" t="s">
         <v>10</v>
@@ -8576,7 +8573,7 @@
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>228</v>
@@ -8607,7 +8604,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L123" s="3" t="s">
         <v>10</v>
@@ -8621,7 +8618,7 @@
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>229</v>
@@ -8652,7 +8649,7 @@
         <v>0</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L124" s="3" t="s">
         <v>10</v>
@@ -8666,7 +8663,7 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="B125" s="18" t="s">
         <v>231</v>
@@ -8711,7 +8708,7 @@
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="B126" s="18" t="s">
         <v>231</v>
@@ -8742,7 +8739,7 @@
         <v>4</v>
       </c>
       <c r="K126" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L126" s="3" t="s">
         <v>10</v>
@@ -8756,7 +8753,7 @@
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>233</v>
@@ -8801,7 +8798,7 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>238</v>
@@ -8846,7 +8843,7 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>240</v>
@@ -8891,7 +8888,7 @@
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>241</v>
@@ -8936,7 +8933,7 @@
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>242</v>
@@ -8981,7 +8978,7 @@
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>243</v>
@@ -9026,7 +9023,7 @@
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>244</v>
@@ -9071,7 +9068,7 @@
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>245</v>
@@ -9116,7 +9113,7 @@
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>246</v>
@@ -9161,7 +9158,7 @@
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>247</v>
@@ -9206,7 +9203,7 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>248</v>
@@ -9251,7 +9248,7 @@
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>249</v>
@@ -9296,7 +9293,7 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>250</v>
@@ -9341,7 +9338,7 @@
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>252</v>
@@ -9386,7 +9383,7 @@
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>254</v>
@@ -9431,7 +9428,7 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>256</v>
@@ -9476,7 +9473,7 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>258</v>
@@ -9521,7 +9518,7 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>260</v>
@@ -9566,7 +9563,7 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>261</v>
@@ -9611,7 +9608,7 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>262</v>
@@ -9656,7 +9653,7 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>263</v>
@@ -9701,7 +9698,7 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>264</v>
@@ -9746,7 +9743,7 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>265</v>
@@ -9791,7 +9788,7 @@
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>266</v>
@@ -9836,7 +9833,7 @@
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>267</v>
@@ -9881,7 +9878,7 @@
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>268</v>
@@ -9926,7 +9923,7 @@
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>269</v>
@@ -9971,7 +9968,7 @@
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>270</v>
@@ -10016,7 +10013,7 @@
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>271</v>
@@ -10061,7 +10058,7 @@
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>272</v>
@@ -10106,7 +10103,7 @@
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>273</v>
@@ -10151,7 +10148,7 @@
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>274</v>
@@ -10196,7 +10193,7 @@
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>276</v>
@@ -10241,7 +10238,7 @@
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>277</v>
@@ -10286,7 +10283,7 @@
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>279</v>
@@ -10331,7 +10328,7 @@
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>281</v>
@@ -10376,7 +10373,7 @@
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>282</v>
@@ -10421,7 +10418,7 @@
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>283</v>
@@ -10466,7 +10463,7 @@
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>284</v>
@@ -10511,7 +10508,7 @@
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>285</v>
@@ -10556,7 +10553,7 @@
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>286</v>
@@ -10601,7 +10598,7 @@
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>287</v>
@@ -10646,7 +10643,7 @@
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>288</v>
@@ -10691,7 +10688,7 @@
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>289</v>
@@ -10736,7 +10733,7 @@
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>291</v>
@@ -10781,7 +10778,7 @@
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>292</v>
@@ -10826,7 +10823,7 @@
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>294</v>
@@ -10871,7 +10868,7 @@
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>295</v>
@@ -10916,7 +10913,7 @@
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>297</v>
@@ -10961,7 +10958,7 @@
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>298</v>
@@ -11006,7 +11003,7 @@
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>299</v>
@@ -11051,7 +11048,7 @@
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>300</v>
@@ -11096,7 +11093,7 @@
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>105</v>
@@ -11141,7 +11138,7 @@
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>301</v>
@@ -11186,7 +11183,7 @@
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>302</v>
@@ -11231,7 +11228,7 @@
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>303</v>
@@ -11276,7 +11273,7 @@
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>304</v>
@@ -11321,7 +11318,7 @@
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>28</v>
@@ -11366,7 +11363,7 @@
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>305</v>
@@ -11411,7 +11408,7 @@
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>306</v>
@@ -11456,7 +11453,7 @@
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>307</v>
@@ -11501,7 +11498,7 @@
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>308</v>
@@ -11546,7 +11543,7 @@
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A189" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>310</v>
@@ -11591,7 +11588,7 @@
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A190" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>311</v>
@@ -11636,7 +11633,7 @@
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A191" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>313</v>
@@ -11681,7 +11678,7 @@
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A192" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>314</v>
@@ -11726,7 +11723,7 @@
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A193" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>316</v>
@@ -11771,7 +11768,7 @@
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A194" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>317</v>
@@ -11816,7 +11813,7 @@
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A195" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>318</v>
@@ -11861,7 +11858,7 @@
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A196" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>319</v>
@@ -11906,7 +11903,7 @@
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A197" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>321</v>
@@ -11951,7 +11948,7 @@
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A198" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>323</v>
@@ -11996,7 +11993,7 @@
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A199" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>324</v>
@@ -12041,7 +12038,7 @@
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A200" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>325</v>
@@ -12086,7 +12083,7 @@
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A201" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>326</v>
@@ -12131,7 +12128,7 @@
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A202" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>327</v>
@@ -12176,7 +12173,7 @@
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A203" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>328</v>
@@ -12221,7 +12218,7 @@
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A204" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>329</v>
@@ -12266,7 +12263,7 @@
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A205" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>330</v>
@@ -12311,7 +12308,7 @@
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A206" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>331</v>
@@ -12356,7 +12353,7 @@
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A207" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>332</v>
@@ -12401,7 +12398,7 @@
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A208" s="4" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>333</v>
@@ -12432,24 +12429,24 @@
         <v>0</v>
       </c>
       <c r="K208" s="3" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="L208" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="M208" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="M208" s="3" t="s">
+      <c r="N208" s="6" t="s">
         <v>335</v>
-      </c>
-      <c r="N208" s="6" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A209" s="4" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C209" s="3" t="s">
         <v>44</v>
@@ -12477,24 +12474,24 @@
         <v>0</v>
       </c>
       <c r="K209" s="3" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="L209" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="M209" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="M209" s="3" t="s">
+      <c r="N209" s="6" t="s">
         <v>335</v>
-      </c>
-      <c r="N209" s="6" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A210" s="4" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C210" s="3" t="s">
         <v>44</v>
@@ -12522,24 +12519,24 @@
         <v>0</v>
       </c>
       <c r="K210" s="3" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="L210" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="M210" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="M210" s="3" t="s">
+      <c r="N210" s="6" t="s">
         <v>335</v>
-      </c>
-      <c r="N210" s="6" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A211" s="4" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C211" s="3" t="s">
         <v>44</v>
@@ -12567,24 +12564,24 @@
         <v>0</v>
       </c>
       <c r="K211" s="3" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="L211" s="3" t="s">
-        <v>334</v>
+        <v>755</v>
       </c>
       <c r="M211" s="3" t="s">
         <v>21</v>
       </c>
       <c r="N211" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A212" s="4" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C212" s="3" t="s">
         <v>81</v>
@@ -12606,30 +12603,30 @@
         <v>63</v>
       </c>
       <c r="I212" s="10" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="J212" s="5">
         <v>42</v>
       </c>
       <c r="K212" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L212" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M212" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="N212" s="7" t="s">
         <v>341</v>
-      </c>
-      <c r="N212" s="7" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A213" s="4" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C213" s="3" t="s">
         <v>81</v>
@@ -12651,7 +12648,7 @@
         <v>23</v>
       </c>
       <c r="I213" s="10" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="J213" s="5">
         <v>10</v>
@@ -12660,21 +12657,21 @@
         <v>221</v>
       </c>
       <c r="L213" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="M213" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="M213" s="3" t="s">
-        <v>344</v>
-      </c>
       <c r="N213" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A214" s="4" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C214" s="3" t="s">
         <v>29</v>
@@ -12696,13 +12693,13 @@
         <v>37</v>
       </c>
       <c r="I214" s="10" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="J214" s="5">
         <v>29</v>
       </c>
       <c r="K214" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L214" s="3" t="s">
         <v>10</v>
@@ -12711,15 +12708,15 @@
         <v>21</v>
       </c>
       <c r="N214" s="17" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A215" s="4" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C215" s="3" t="s">
         <v>29</v>
@@ -12741,14 +12738,14 @@
         <v>90</v>
       </c>
       <c r="I215" s="10" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="J215" s="5">
         <f>17+22</f>
         <v>39</v>
       </c>
       <c r="K215" s="3" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="L215" s="3" t="s">
         <v>10</v>
@@ -12757,15 +12754,15 @@
         <v>21</v>
       </c>
       <c r="N215" s="17" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A216" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C216" s="3" t="s">
         <v>29</v>
@@ -12793,24 +12790,24 @@
         <v>0</v>
       </c>
       <c r="K216" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L216" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M216" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N216" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N216" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A217" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C217" s="3" t="s">
         <v>29</v>
@@ -12832,30 +12829,30 @@
         <v>19</v>
       </c>
       <c r="I217" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J217" s="5">
         <v>58</v>
       </c>
       <c r="K217" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L217" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M217" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N217" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N217" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A218" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C218" s="3" t="s">
         <v>29</v>
@@ -12883,24 +12880,24 @@
         <v>0</v>
       </c>
       <c r="K218" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L218" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M218" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N218" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N218" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A219" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C219" s="3" t="s">
         <v>29</v>
@@ -12928,24 +12925,24 @@
         <v>0</v>
       </c>
       <c r="K219" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L219" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M219" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N219" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N219" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A220" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C220" s="3" t="s">
         <v>29</v>
@@ -12967,30 +12964,30 @@
         <v>71</v>
       </c>
       <c r="I220" s="10" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="J220" s="5">
         <v>38</v>
       </c>
       <c r="K220" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L220" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M220" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N220" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N220" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A221" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C221" s="3" t="s">
         <v>29</v>
@@ -13012,30 +13009,30 @@
         <v>170</v>
       </c>
       <c r="I221" s="10" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="J221" s="5">
         <v>5</v>
       </c>
       <c r="K221" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L221" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M221" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N221" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N221" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A222" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C222" s="3" t="s">
         <v>29</v>
@@ -13063,24 +13060,24 @@
         <v>0</v>
       </c>
       <c r="K222" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L222" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M222" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N222" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N222" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A223" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C223" s="3" t="s">
         <v>29</v>
@@ -13102,30 +13099,30 @@
         <v>60</v>
       </c>
       <c r="I223" s="10" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="J223" s="5">
         <v>71</v>
       </c>
       <c r="K223" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L223" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M223" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N223" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N223" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A224" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C224" s="3" t="s">
         <v>29</v>
@@ -13147,30 +13144,30 @@
         <v>10</v>
       </c>
       <c r="I224" s="10" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="J224" s="5">
         <v>59</v>
       </c>
       <c r="K224" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L224" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M224" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N224" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N224" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A225" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C225" s="3" t="s">
         <v>29</v>
@@ -13192,30 +13189,30 @@
         <v>31</v>
       </c>
       <c r="I225" s="10" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="J225" s="5">
         <v>73</v>
       </c>
       <c r="K225" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L225" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M225" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N225" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N225" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A226" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C226" s="3" t="s">
         <v>29</v>
@@ -13237,30 +13234,30 @@
         <v>36</v>
       </c>
       <c r="I226" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J226" s="5">
         <v>20</v>
       </c>
       <c r="K226" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L226" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M226" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N226" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N226" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A227" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C227" s="3" t="s">
         <v>29</v>
@@ -13282,30 +13279,30 @@
         <v>53</v>
       </c>
       <c r="I227" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J227" s="5">
         <v>2</v>
       </c>
       <c r="K227" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L227" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M227" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N227" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N227" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A228" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C228" s="3" t="s">
         <v>29</v>
@@ -13333,24 +13330,24 @@
         <v>0</v>
       </c>
       <c r="K228" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L228" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M228" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N228" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N228" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A229" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C229" s="3" t="s">
         <v>29</v>
@@ -13378,24 +13375,24 @@
         <v>0</v>
       </c>
       <c r="K229" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L229" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M229" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N229" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N229" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A230" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C230" s="3" t="s">
         <v>29</v>
@@ -13423,24 +13420,24 @@
         <v>0</v>
       </c>
       <c r="K230" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L230" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M230" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N230" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N230" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A231" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C231" s="3" t="s">
         <v>29</v>
@@ -13468,24 +13465,24 @@
         <v>0</v>
       </c>
       <c r="K231" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L231" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M231" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N231" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N231" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A232" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C232" s="3" t="s">
         <v>29</v>
@@ -13513,24 +13510,24 @@
         <v>0</v>
       </c>
       <c r="K232" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L232" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M232" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N232" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N232" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A233" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C233" s="3" t="s">
         <v>29</v>
@@ -13558,24 +13555,24 @@
         <v>0</v>
       </c>
       <c r="K233" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L233" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M233" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N233" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N233" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A234" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C234" s="3" t="s">
         <v>29</v>
@@ -13603,24 +13600,24 @@
         <v>0</v>
       </c>
       <c r="K234" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L234" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M234" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N234" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N234" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A235" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C235" s="3" t="s">
         <v>29</v>
@@ -13648,24 +13645,24 @@
         <v>0</v>
       </c>
       <c r="K235" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L235" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M235" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N235" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N235" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A236" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C236" s="3" t="s">
         <v>29</v>
@@ -13693,24 +13690,24 @@
         <v>0</v>
       </c>
       <c r="K236" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L236" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M236" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N236" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N236" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A237" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C237" s="3" t="s">
         <v>29</v>
@@ -13738,24 +13735,24 @@
         <v>0</v>
       </c>
       <c r="K237" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L237" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M237" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N237" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N237" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A238" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C238" s="3" t="s">
         <v>29</v>
@@ -13777,30 +13774,30 @@
         <v>37</v>
       </c>
       <c r="I238" s="10" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="J238" s="5">
         <v>37</v>
       </c>
       <c r="K238" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L238" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M238" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N238" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N238" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A239" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C239" s="3" t="s">
         <v>29</v>
@@ -13822,30 +13819,30 @@
         <v>5</v>
       </c>
       <c r="I239" s="10" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="J239" s="5">
         <v>34</v>
       </c>
       <c r="K239" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L239" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M239" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N239" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N239" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A240" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C240" s="3" t="s">
         <v>29</v>
@@ -13867,30 +13864,30 @@
         <v>79</v>
       </c>
       <c r="I240" s="10" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="J240" s="5">
         <v>19</v>
       </c>
       <c r="K240" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L240" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M240" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N240" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N240" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A241" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C241" s="3" t="s">
         <v>29</v>
@@ -13912,30 +13909,30 @@
         <v>23</v>
       </c>
       <c r="I241" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J241" s="5">
         <v>54</v>
       </c>
       <c r="K241" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L241" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M241" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N241" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N241" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A242" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C242" s="3" t="s">
         <v>29</v>
@@ -13963,24 +13960,24 @@
         <v>0</v>
       </c>
       <c r="K242" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L242" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M242" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N242" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N242" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A243" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C243" s="3" t="s">
         <v>29</v>
@@ -14008,24 +14005,24 @@
         <v>0</v>
       </c>
       <c r="K243" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L243" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M243" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N243" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N243" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A244" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C244" s="3" t="s">
         <v>29</v>
@@ -14053,24 +14050,24 @@
         <v>0</v>
       </c>
       <c r="K244" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L244" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M244" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N244" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N244" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A245" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C245" s="3" t="s">
         <v>29</v>
@@ -14092,27 +14089,27 @@
         <v>11</v>
       </c>
       <c r="I245" s="10" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="J245" s="5">
         <v>87</v>
       </c>
       <c r="K245" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L245" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M245" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N245" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N245" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A246" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>303</v>
@@ -14143,24 +14140,24 @@
         <v>25</v>
       </c>
       <c r="K246" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L246" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M246" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N246" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N246" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A247" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C247" s="3" t="s">
         <v>29</v>
@@ -14188,24 +14185,24 @@
         <v>0</v>
       </c>
       <c r="K247" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L247" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M247" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N247" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N247" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A248" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C248" s="3" t="s">
         <v>29</v>
@@ -14233,24 +14230,24 @@
         <v>0</v>
       </c>
       <c r="K248" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L248" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M248" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N248" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N248" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A249" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C249" s="3" t="s">
         <v>29</v>
@@ -14272,30 +14269,30 @@
         <v>6</v>
       </c>
       <c r="I249" s="10" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J249" s="5">
         <v>30</v>
       </c>
       <c r="K249" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L249" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M249" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N249" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N249" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A250" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C250" s="3" t="s">
         <v>29</v>
@@ -14317,31 +14314,31 @@
         <v>43</v>
       </c>
       <c r="I250" s="10" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="J250" s="5">
         <f>16+8+15+12</f>
         <v>51</v>
       </c>
       <c r="K250" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L250" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M250" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N250" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N250" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A251" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C251" s="3" t="s">
         <v>29</v>
@@ -14363,30 +14360,30 @@
         <v>40</v>
       </c>
       <c r="I251" s="10" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J251" s="5">
         <v>6</v>
       </c>
       <c r="K251" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L251" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M251" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N251" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N251" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A252" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C252" s="3" t="s">
         <v>29</v>
@@ -14414,24 +14411,24 @@
         <v>0</v>
       </c>
       <c r="K252" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L252" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M252" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N252" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N252" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A253" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C253" s="3" t="s">
         <v>29</v>
@@ -14459,24 +14456,24 @@
         <v>0</v>
       </c>
       <c r="K253" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L253" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M253" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N253" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N253" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A254" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C254" s="3" t="s">
         <v>29</v>
@@ -14504,24 +14501,24 @@
         <v>0</v>
       </c>
       <c r="K254" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L254" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M254" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N254" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="N254" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A255" s="4" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C255" s="3" t="s">
         <v>29</v>
@@ -14555,18 +14552,18 @@
         <v>10</v>
       </c>
       <c r="M255" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N255" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A256" s="4" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C256" s="3" t="s">
         <v>29</v>
@@ -14594,24 +14591,24 @@
         <v>0</v>
       </c>
       <c r="K256" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L256" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M256" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N256" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="257" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A257" s="4" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C257" s="3" t="s">
         <v>29</v>
@@ -14639,24 +14636,24 @@
         <v>0</v>
       </c>
       <c r="K257" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L257" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M257" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N257" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="258" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A258" s="4" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C258" s="3" t="s">
         <v>29</v>
@@ -14690,18 +14687,18 @@
         <v>10</v>
       </c>
       <c r="M258" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N258" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="259" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A259" s="4" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C259" s="3" t="s">
         <v>29</v>
@@ -14729,24 +14726,24 @@
         <v>0</v>
       </c>
       <c r="K259" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L259" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M259" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N259" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="260" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A260" s="4" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C260" s="3" t="s">
         <v>29</v>
@@ -14774,7 +14771,7 @@
         <v>0</v>
       </c>
       <c r="K260" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L260" s="3" t="s">
         <v>10</v>
@@ -14783,15 +14780,15 @@
         <v>120</v>
       </c>
       <c r="N260" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="261" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A261" s="4" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C261" s="3" t="s">
         <v>81</v>
@@ -14819,7 +14816,7 @@
         <v>0</v>
       </c>
       <c r="K261" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L261" s="3" t="s">
         <v>10</v>
@@ -14828,15 +14825,15 @@
         <v>30</v>
       </c>
       <c r="N261" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="262" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A262" s="4" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C262" s="3" t="s">
         <v>29</v>
@@ -14858,13 +14855,13 @@
         <v>2</v>
       </c>
       <c r="I262" s="3" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="J262" s="5">
         <v>32</v>
       </c>
       <c r="K262" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L262" s="3" t="s">
         <v>10</v>
@@ -14873,15 +14870,15 @@
         <v>30</v>
       </c>
       <c r="N262" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="263" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A263" s="4" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C263" s="3" t="s">
         <v>29</v>
@@ -14903,13 +14900,13 @@
         <v>2</v>
       </c>
       <c r="I263" s="3" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="J263" s="5">
         <v>18</v>
       </c>
       <c r="K263" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L263" s="3" t="s">
         <v>10</v>
@@ -14918,15 +14915,15 @@
         <v>30</v>
       </c>
       <c r="N263" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="264" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A264" s="4" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C264" s="3" t="s">
         <v>29</v>
@@ -14954,7 +14951,7 @@
         <v>0</v>
       </c>
       <c r="K264" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L264" s="3" t="s">
         <v>10</v>
@@ -14963,15 +14960,15 @@
         <v>30</v>
       </c>
       <c r="N264" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="265" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A265" s="4" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C265" s="3" t="s">
         <v>29</v>
@@ -14999,7 +14996,7 @@
         <v>0</v>
       </c>
       <c r="K265" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L265" s="3" t="s">
         <v>10</v>
@@ -15008,15 +15005,15 @@
         <v>30</v>
       </c>
       <c r="N265" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="266" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A266" s="4" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C266" s="3" t="s">
         <v>29</v>
@@ -15044,7 +15041,7 @@
         <v>0</v>
       </c>
       <c r="K266" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L266" s="3" t="s">
         <v>10</v>
@@ -15053,12 +15050,12 @@
         <v>30</v>
       </c>
       <c r="N266" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="267" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A267" s="4" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>225</v>
@@ -15089,7 +15086,7 @@
         <v>0</v>
       </c>
       <c r="K267" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L267" s="3" t="s">
         <v>10</v>
@@ -15098,15 +15095,15 @@
         <v>30</v>
       </c>
       <c r="N267" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="268" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A268" s="19" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B268" s="20" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C268" s="3" t="s">
         <v>135</v>
@@ -15128,13 +15125,13 @@
         <v>50</v>
       </c>
       <c r="I268" s="11" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="J268" s="13">
         <v>12</v>
       </c>
       <c r="K268" s="11" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L268" s="3" t="s">
         <v>10</v>
@@ -15143,7 +15140,7 @@
         <v>120</v>
       </c>
       <c r="N268" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="O268" s="15"/>
       <c r="P268" s="15"/>
@@ -15156,10 +15153,10 @@
     </row>
     <row r="269" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A269" s="19" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B269" s="20" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C269" s="3" t="s">
         <v>135</v>
@@ -15181,7 +15178,7 @@
         <v>21</v>
       </c>
       <c r="I269" s="11" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="J269" s="13">
         <v>3</v>
@@ -15196,7 +15193,7 @@
         <v>120</v>
       </c>
       <c r="N269" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="O269" s="15"/>
       <c r="P269" s="15"/>
@@ -15209,10 +15206,10 @@
     </row>
     <row r="270" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A270" s="19" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B270" s="20" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C270" s="3" t="s">
         <v>135</v>
@@ -15249,7 +15246,7 @@
         <v>120</v>
       </c>
       <c r="N270" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="O270" s="15"/>
       <c r="P270" s="15"/>
@@ -15262,10 +15259,10 @@
     </row>
     <row r="271" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A271" s="19" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C271" s="3" t="s">
         <v>29</v>
@@ -15287,22 +15284,22 @@
         <v>7</v>
       </c>
       <c r="I271" s="11" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="J271" s="13">
         <v>24</v>
       </c>
       <c r="K271" s="11" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L271" s="11" t="s">
         <v>30</v>
       </c>
       <c r="M271" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="N271" s="7" t="s">
         <v>412</v>
-      </c>
-      <c r="N271" s="7" t="s">
-        <v>413</v>
       </c>
       <c r="O271" s="15"/>
       <c r="P271" s="15"/>
@@ -15315,10 +15312,10 @@
     </row>
     <row r="272" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A272" s="19" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B272" s="20" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C272" s="3" t="s">
         <v>29</v>
@@ -15340,22 +15337,22 @@
         <v>1.42</v>
       </c>
       <c r="I272" s="11" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J272" s="13">
         <v>1.58</v>
       </c>
       <c r="K272" s="11" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L272" s="11" t="s">
         <v>30</v>
       </c>
       <c r="M272" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N272" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O272" s="15"/>
       <c r="P272" s="15"/>
@@ -15368,10 +15365,10 @@
     </row>
     <row r="273" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A273" s="19" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C273" s="3" t="s">
         <v>29</v>
@@ -15393,7 +15390,7 @@
         <v>8.9000000000000057</v>
       </c>
       <c r="I273" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="J273" s="13">
         <v>68.099999999999994</v>
@@ -15405,10 +15402,10 @@
         <v>30</v>
       </c>
       <c r="M273" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="N273" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O273" s="15"/>
       <c r="P273" s="15"/>
@@ -15421,10 +15418,10 @@
     </row>
     <row r="274" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A274" s="4" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C274" s="3" t="s">
         <v>44</v>
@@ -15461,15 +15458,15 @@
         <v>236</v>
       </c>
       <c r="N274" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="275" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A275" s="4" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C275" s="3" t="s">
         <v>44</v>
@@ -15506,15 +15503,15 @@
         <v>236</v>
       </c>
       <c r="N275" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="276" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A276" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C276" s="3" t="s">
         <v>44</v>
@@ -15551,15 +15548,15 @@
         <v>236</v>
       </c>
       <c r="N276" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="277" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A277" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C277" s="3" t="s">
         <v>44</v>
@@ -15596,15 +15593,15 @@
         <v>236</v>
       </c>
       <c r="N277" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="278" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A278" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C278" s="3" t="s">
         <v>44</v>
@@ -15641,15 +15638,15 @@
         <v>236</v>
       </c>
       <c r="N278" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="279" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A279" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C279" s="3" t="s">
         <v>44</v>
@@ -15686,15 +15683,15 @@
         <v>236</v>
       </c>
       <c r="N279" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="280" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A280" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C280" s="3" t="s">
         <v>44</v>
@@ -15731,15 +15728,15 @@
         <v>236</v>
       </c>
       <c r="N280" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="281" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A281" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C281" s="3" t="s">
         <v>44</v>
@@ -15776,15 +15773,15 @@
         <v>236</v>
       </c>
       <c r="N281" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="282" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A282" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C282" s="3" t="s">
         <v>44</v>
@@ -15821,15 +15818,15 @@
         <v>236</v>
       </c>
       <c r="N282" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="283" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A283" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C283" s="3" t="s">
         <v>44</v>
@@ -15866,15 +15863,15 @@
         <v>236</v>
       </c>
       <c r="N283" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="284" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A284" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C284" s="3" t="s">
         <v>44</v>
@@ -15911,15 +15908,15 @@
         <v>236</v>
       </c>
       <c r="N284" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="285" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A285" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C285" s="3" t="s">
         <v>44</v>
@@ -15956,15 +15953,15 @@
         <v>236</v>
       </c>
       <c r="N285" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="286" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A286" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C286" s="3" t="s">
         <v>44</v>
@@ -16001,15 +15998,15 @@
         <v>236</v>
       </c>
       <c r="N286" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="287" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A287" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C287" s="3" t="s">
         <v>44</v>
@@ -16046,15 +16043,15 @@
         <v>236</v>
       </c>
       <c r="N287" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="288" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A288" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C288" s="3" t="s">
         <v>44</v>
@@ -16091,15 +16088,15 @@
         <v>236</v>
       </c>
       <c r="N288" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A289" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C289" s="3" t="s">
         <v>44</v>
@@ -16136,15 +16133,15 @@
         <v>236</v>
       </c>
       <c r="N289" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A290" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C290" s="3" t="s">
         <v>44</v>
@@ -16181,15 +16178,15 @@
         <v>236</v>
       </c>
       <c r="N290" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A291" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C291" s="3" t="s">
         <v>44</v>
@@ -16226,12 +16223,12 @@
         <v>236</v>
       </c>
       <c r="N291" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A292" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>166</v>
@@ -16271,12 +16268,12 @@
         <v>236</v>
       </c>
       <c r="N292" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A293" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B293" s="3" t="s">
         <v>164</v>
@@ -16316,12 +16313,12 @@
         <v>236</v>
       </c>
       <c r="N293" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A294" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B294" s="3" t="s">
         <v>162</v>
@@ -16361,15 +16358,15 @@
         <v>236</v>
       </c>
       <c r="N294" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A295" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C295" s="3" t="s">
         <v>44</v>
@@ -16406,15 +16403,15 @@
         <v>236</v>
       </c>
       <c r="N295" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A296" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C296" s="3" t="s">
         <v>44</v>
@@ -16451,15 +16448,15 @@
         <v>236</v>
       </c>
       <c r="N296" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A297" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C297" s="3" t="s">
         <v>44</v>
@@ -16496,15 +16493,15 @@
         <v>236</v>
       </c>
       <c r="N297" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A298" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C298" s="3" t="s">
         <v>44</v>
@@ -16541,15 +16538,15 @@
         <v>236</v>
       </c>
       <c r="N298" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A299" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C299" s="3" t="s">
         <v>44</v>
@@ -16586,15 +16583,15 @@
         <v>236</v>
       </c>
       <c r="N299" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A300" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C300" s="3" t="s">
         <v>44</v>
@@ -16631,15 +16628,15 @@
         <v>236</v>
       </c>
       <c r="N300" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A301" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C301" s="3" t="s">
         <v>44</v>
@@ -16676,15 +16673,15 @@
         <v>236</v>
       </c>
       <c r="N301" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A302" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C302" s="3" t="s">
         <v>19</v>
@@ -16721,15 +16718,15 @@
         <v>236</v>
       </c>
       <c r="N302" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A303" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C303" s="3" t="s">
         <v>44</v>
@@ -16766,15 +16763,15 @@
         <v>236</v>
       </c>
       <c r="N303" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A304" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C304" s="3" t="s">
         <v>44</v>
@@ -16811,15 +16808,15 @@
         <v>236</v>
       </c>
       <c r="N304" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A305" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C305" s="3" t="s">
         <v>44</v>
@@ -16856,15 +16853,15 @@
         <v>236</v>
       </c>
       <c r="N305" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A306" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C306" s="3" t="s">
         <v>44</v>
@@ -16901,15 +16898,15 @@
         <v>236</v>
       </c>
       <c r="N306" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A307" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C307" s="3" t="s">
         <v>44</v>
@@ -16946,15 +16943,15 @@
         <v>236</v>
       </c>
       <c r="N307" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A308" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C308" s="3" t="s">
         <v>44</v>
@@ -16991,15 +16988,15 @@
         <v>236</v>
       </c>
       <c r="N308" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A309" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C309" s="3" t="s">
         <v>44</v>
@@ -17036,15 +17033,15 @@
         <v>236</v>
       </c>
       <c r="N309" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A310" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C310" s="3" t="s">
         <v>44</v>
@@ -17081,15 +17078,15 @@
         <v>236</v>
       </c>
       <c r="N310" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A311" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C311" s="3" t="s">
         <v>44</v>
@@ -17126,15 +17123,15 @@
         <v>236</v>
       </c>
       <c r="N311" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A312" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C312" s="3" t="s">
         <v>44</v>
@@ -17171,12 +17168,12 @@
         <v>236</v>
       </c>
       <c r="N312" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A313" s="4" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>37</v>
@@ -17213,15 +17210,15 @@
         <v>194</v>
       </c>
       <c r="M313" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="N313" s="6" t="s">
         <v>455</v>
-      </c>
-      <c r="N313" s="6" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A314" s="4" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>37</v>
@@ -17246,13 +17243,13 @@
         <v>20</v>
       </c>
       <c r="I314" s="10" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="J314" s="5">
         <v>3</v>
       </c>
       <c r="K314" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L314" s="3" t="s">
         <v>10</v>
@@ -17261,15 +17258,15 @@
         <v>120</v>
       </c>
       <c r="N314" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A315" s="4" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C315" s="3" t="s">
         <v>29</v>
@@ -17300,21 +17297,21 @@
         <v>221</v>
       </c>
       <c r="L315" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="M315" s="3" t="s">
         <v>21</v>
       </c>
       <c r="N315" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A316" s="4" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C316" s="3" t="s">
         <v>29</v>
@@ -17342,7 +17339,7 @@
         <v>0</v>
       </c>
       <c r="K316" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L316" s="3" t="s">
         <v>10</v>
@@ -17351,15 +17348,15 @@
         <v>21</v>
       </c>
       <c r="N316" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A317" s="4" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C317" s="3" t="s">
         <v>29</v>
@@ -17381,13 +17378,13 @@
         <v>7</v>
       </c>
       <c r="I317" s="10" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="J317" s="5">
         <v>70</v>
       </c>
       <c r="K317" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L317" s="3" t="s">
         <v>10</v>
@@ -17396,15 +17393,15 @@
         <v>236</v>
       </c>
       <c r="N317" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A318" s="4" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C318" s="3" t="s">
         <v>29</v>
@@ -17432,7 +17429,7 @@
         <v>0</v>
       </c>
       <c r="K318" s="3" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="L318" s="3" t="s">
         <v>10</v>
@@ -17441,15 +17438,15 @@
         <v>21</v>
       </c>
       <c r="N318" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A319" s="4" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C319" s="3" t="s">
         <v>81</v>
@@ -17471,14 +17468,14 @@
         <v>5</v>
       </c>
       <c r="I319" s="10" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="J319" s="5">
         <f>98+33</f>
         <v>131</v>
       </c>
       <c r="K319" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L319" s="3" t="s">
         <v>10</v>
@@ -17487,15 +17484,15 @@
         <v>30</v>
       </c>
       <c r="N319" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A320" s="4" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C320" s="3" t="s">
         <v>81</v>
@@ -17517,7 +17514,7 @@
         <v>24</v>
       </c>
       <c r="I320" s="10" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="J320" s="5">
         <v>56</v>
@@ -17529,18 +17526,18 @@
         <v>153</v>
       </c>
       <c r="M320" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="N320" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="321" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A321" s="4" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C321" s="3" t="s">
         <v>81</v>
@@ -17568,7 +17565,7 @@
         <v>0</v>
       </c>
       <c r="K321" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L321" s="3" t="s">
         <v>10</v>
@@ -17577,15 +17574,15 @@
         <v>30</v>
       </c>
       <c r="N321" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="322" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A322" s="4" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C322" s="3" t="s">
         <v>81</v>
@@ -17607,7 +17604,7 @@
         <v>8</v>
       </c>
       <c r="I322" s="10" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="J322" s="5">
         <f>31+20+6</f>
@@ -17620,18 +17617,18 @@
         <v>153</v>
       </c>
       <c r="M322" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="N322" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="323" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A323" s="4" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C323" s="3" t="s">
         <v>81</v>
@@ -17653,13 +17650,13 @@
         <v>2</v>
       </c>
       <c r="I323" s="10" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="J323" s="5">
         <v>19</v>
       </c>
       <c r="K323" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L323" s="3" t="s">
         <v>10</v>
@@ -17668,15 +17665,15 @@
         <v>30</v>
       </c>
       <c r="N323" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="324" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A324" s="4" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C324" s="3" t="s">
         <v>81</v>
@@ -17698,7 +17695,7 @@
         <v>11</v>
       </c>
       <c r="I324" s="10" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="J324" s="5">
         <f>1+30+1+18+4+4</f>
@@ -17711,18 +17708,18 @@
         <v>153</v>
       </c>
       <c r="M324" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="N324" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="325" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A325" s="4" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C325" s="3" t="s">
         <v>176</v>
@@ -17750,24 +17747,24 @@
         <v>0</v>
       </c>
       <c r="K325" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L325" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M325" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="N325" s="6" t="s">
         <v>466</v>
-      </c>
-      <c r="N325" s="6" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="326" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A326" s="4" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C326" s="3" t="s">
         <v>176</v>
@@ -17789,31 +17786,31 @@
         <v>47.917864476386036</v>
       </c>
       <c r="I326" s="10" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="J326" s="5">
         <f>3+(30/365.25)</f>
         <v>3.0821355236139629</v>
       </c>
       <c r="K326" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L326" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M326" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N326" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="327" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A327" s="4" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C327" s="3" t="s">
         <v>176</v>
@@ -17835,7 +17832,7 @@
         <v>51.915126625598901</v>
       </c>
       <c r="I327" s="3" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="J327" s="5">
         <f>3+((31+30+31+30)/365.25)+4-((30+31+30)/365.25)+4</f>
@@ -17851,15 +17848,15 @@
         <v>21</v>
       </c>
       <c r="N327" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="328" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A328" s="4" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B328" s="20" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C328" s="3" t="s">
         <v>176</v>
@@ -17893,18 +17890,18 @@
         <v>10</v>
       </c>
       <c r="M328" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="N328" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="329" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A329" s="4" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C329" s="3" t="s">
         <v>176</v>
@@ -17941,15 +17938,15 @@
         <v>21</v>
       </c>
       <c r="N329" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="330" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A330" s="4" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C330" s="3" t="s">
         <v>176</v>
@@ -17971,30 +17968,30 @@
         <v>44</v>
       </c>
       <c r="I330" s="10" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="J330" s="5">
         <v>5</v>
       </c>
       <c r="K330" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L330" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M330" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N330" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="331" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A331" s="4" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C331" s="3" t="s">
         <v>176</v>
@@ -18022,24 +18019,24 @@
         <v>0</v>
       </c>
       <c r="K331" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L331" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M331" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N331" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="332" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A332" s="4" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C332" s="3" t="s">
         <v>176</v>
@@ -18067,24 +18064,24 @@
         <v>0</v>
       </c>
       <c r="K332" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L332" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M332" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N332" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="333" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A333" s="4" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C333" s="3" t="s">
         <v>44</v>
@@ -18106,7 +18103,7 @@
         <v>4</v>
       </c>
       <c r="I333" s="10" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="J333" s="5">
         <v>49</v>
@@ -18115,21 +18112,21 @@
         <v>221</v>
       </c>
       <c r="L333" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="M333" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="N333" s="6" t="s">
         <v>478</v>
-      </c>
-      <c r="M333" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="N333" s="6" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="334" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A334" s="4" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C334" s="3" t="s">
         <v>44</v>
@@ -18151,7 +18148,7 @@
         <v>36</v>
       </c>
       <c r="I334" s="10" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="J334" s="5">
         <v>3</v>
@@ -18160,21 +18157,21 @@
         <v>221</v>
       </c>
       <c r="L334" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="M334" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="N334" s="6" t="s">
         <v>478</v>
-      </c>
-      <c r="M334" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="N334" s="6" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="335" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A335" s="4" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C335" s="3" t="s">
         <v>44</v>
@@ -18205,21 +18202,21 @@
         <v>221</v>
       </c>
       <c r="L335" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="M335" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="N335" s="6" t="s">
         <v>478</v>
-      </c>
-      <c r="M335" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="N335" s="6" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="336" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A336" s="4" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C336" s="3" t="s">
         <v>29</v>
@@ -18256,7 +18253,7 @@
         <v>21</v>
       </c>
       <c r="N336" s="7" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="O336" s="15"/>
       <c r="P336" s="15"/>
@@ -18269,10 +18266,10 @@
     </row>
     <row r="337" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A337" s="4" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C337" s="3" t="s">
         <v>29</v>
@@ -18309,7 +18306,7 @@
         <v>120</v>
       </c>
       <c r="N337" s="7" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="O337" s="15"/>
       <c r="P337" s="15"/>
@@ -18322,10 +18319,10 @@
     </row>
     <row r="338" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A338" s="4" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C338" s="3" t="s">
         <v>29</v>
@@ -18347,7 +18344,7 @@
         <v>24</v>
       </c>
       <c r="I338" s="10" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="J338" s="5">
         <v>17</v>
@@ -18362,7 +18359,7 @@
         <v>120</v>
       </c>
       <c r="N338" s="7" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="O338" s="15"/>
       <c r="P338" s="15"/>
@@ -18375,10 +18372,10 @@
     </row>
     <row r="339" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A339" s="4" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C339" s="3" t="s">
         <v>29</v>
@@ -18400,13 +18397,13 @@
         <v>2</v>
       </c>
       <c r="I339" s="10" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="J339" s="5">
         <v>12</v>
       </c>
       <c r="K339" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L339" s="3" t="s">
         <v>10</v>
@@ -18415,7 +18412,7 @@
         <v>30</v>
       </c>
       <c r="N339" s="7" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="O339" s="15"/>
       <c r="P339" s="15"/>
@@ -18428,10 +18425,10 @@
     </row>
     <row r="340" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A340" s="4" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C340" s="3" t="s">
         <v>19</v>
@@ -18459,7 +18456,7 @@
         <v>0.75</v>
       </c>
       <c r="K340" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L340" s="3" t="s">
         <v>10</v>
@@ -18468,7 +18465,7 @@
         <v>21</v>
       </c>
       <c r="N340" s="7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="O340" s="15"/>
       <c r="P340" s="15"/>
@@ -18481,10 +18478,10 @@
     </row>
     <row r="341" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A341" s="4" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C341" s="3" t="s">
         <v>19</v>
@@ -18512,7 +18509,7 @@
         <v>0</v>
       </c>
       <c r="K341" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L341" s="3" t="s">
         <v>10</v>
@@ -18521,7 +18518,7 @@
         <v>21</v>
       </c>
       <c r="N341" s="7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="O341" s="15"/>
       <c r="P341" s="15"/>
@@ -18534,10 +18531,10 @@
     </row>
     <row r="342" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A342" s="21" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="B342" s="22" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C342" s="3" t="s">
         <v>135</v>
@@ -18566,7 +18563,7 @@
         <v>28.256700000000002</v>
       </c>
       <c r="K342" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L342" s="3" t="s">
         <v>10</v>
@@ -18575,7 +18572,7 @@
         <v>236</v>
       </c>
       <c r="N342" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="O342" s="15"/>
       <c r="P342" s="15"/>
@@ -18588,10 +18585,10 @@
     </row>
     <row r="343" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A343" s="21" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="B343" s="20" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C343" s="3" t="s">
         <v>176</v>
@@ -18620,7 +18617,7 @@
         <v>14.850399999999999</v>
       </c>
       <c r="K343" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L343" s="3" t="s">
         <v>10</v>
@@ -18629,7 +18626,7 @@
         <v>236</v>
       </c>
       <c r="N343" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="O343" s="15"/>
       <c r="P343" s="15"/>
@@ -18642,10 +18639,10 @@
     </row>
     <row r="344" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A344" s="21" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="B344" s="20" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C344" s="3" t="s">
         <v>135</v>
@@ -18674,7 +18671,7 @@
         <v>68.674899999999994</v>
       </c>
       <c r="K344" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L344" s="3" t="s">
         <v>10</v>
@@ -18683,7 +18680,7 @@
         <v>236</v>
       </c>
       <c r="N344" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="O344" s="15"/>
       <c r="P344" s="15"/>
@@ -18696,10 +18693,10 @@
     </row>
     <row r="345" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A345" s="21" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="B345" s="20" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C345" s="3" t="s">
         <v>176</v>
@@ -18728,7 +18725,7 @@
         <v>2.4600000000000004</v>
       </c>
       <c r="K345" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L345" s="3" t="s">
         <v>10</v>
@@ -18737,7 +18734,7 @@
         <v>236</v>
       </c>
       <c r="N345" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="O345" s="15"/>
       <c r="P345" s="15"/>
@@ -18750,10 +18747,10 @@
     </row>
     <row r="346" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A346" s="21" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="B346" s="20" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C346" s="3" t="s">
         <v>176</v>
@@ -18782,7 +18779,7 @@
         <v>12.33</v>
       </c>
       <c r="K346" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L346" s="3" t="s">
         <v>10</v>
@@ -18791,7 +18788,7 @@
         <v>236</v>
       </c>
       <c r="N346" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="O346" s="15"/>
       <c r="P346" s="15"/>
@@ -18804,13 +18801,13 @@
     </row>
     <row r="347" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A347" s="21" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="B347" s="20" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D347" s="5">
         <v>43.73</v>
@@ -18836,7 +18833,7 @@
         <v>30.822399999999998</v>
       </c>
       <c r="K347" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L347" s="3" t="s">
         <v>10</v>
@@ -18845,7 +18842,7 @@
         <v>236</v>
       </c>
       <c r="N347" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="O347" s="15"/>
       <c r="P347" s="15"/>
@@ -18858,10 +18855,10 @@
     </row>
     <row r="348" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A348" s="21" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="B348" s="20" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C348" s="3" t="s">
         <v>135</v>
@@ -18890,7 +18887,7 @@
         <v>0.25919999999999999</v>
       </c>
       <c r="K348" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L348" s="3" t="s">
         <v>10</v>
@@ -18899,15 +18896,15 @@
         <v>236</v>
       </c>
       <c r="N348" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="349" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A349" s="21" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="B349" s="20" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C349" s="3" t="s">
         <v>176</v>
@@ -18936,7 +18933,7 @@
         <v>4.2863999999999995</v>
       </c>
       <c r="K349" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L349" s="3" t="s">
         <v>10</v>
@@ -18945,18 +18942,18 @@
         <v>236</v>
       </c>
       <c r="N349" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="350" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A350" s="21" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="B350" s="20" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D350" s="5">
         <v>35.25</v>
@@ -18981,7 +18978,7 @@
         <v>0</v>
       </c>
       <c r="K350" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L350" s="3" t="s">
         <v>10</v>
@@ -18990,15 +18987,15 @@
         <v>236</v>
       </c>
       <c r="N350" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="351" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A351" s="4" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C351" s="3" t="s">
         <v>44</v>
@@ -19026,7 +19023,7 @@
         <v>1</v>
       </c>
       <c r="K351" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L351" s="3" t="s">
         <v>10</v>
@@ -19035,15 +19032,15 @@
         <v>120</v>
       </c>
       <c r="N351" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="352" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A352" s="4" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C352" s="3" t="s">
         <v>44</v>
@@ -19071,7 +19068,7 @@
         <v>1</v>
       </c>
       <c r="K352" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L352" s="3" t="s">
         <v>10</v>
@@ -19080,15 +19077,15 @@
         <v>120</v>
       </c>
       <c r="N352" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A353" s="4" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C353" s="3" t="s">
         <v>44</v>
@@ -19116,7 +19113,7 @@
         <v>0</v>
       </c>
       <c r="K353" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L353" s="3" t="s">
         <v>10</v>
@@ -19125,15 +19122,15 @@
         <v>120</v>
       </c>
       <c r="N353" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A354" s="4" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C354" s="3" t="s">
         <v>44</v>
@@ -19161,7 +19158,7 @@
         <v>0</v>
       </c>
       <c r="K354" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L354" s="3" t="s">
         <v>10</v>
@@ -19170,15 +19167,15 @@
         <v>120</v>
       </c>
       <c r="N354" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A355" s="4" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C355" s="3" t="s">
         <v>44</v>
@@ -19206,7 +19203,7 @@
         <v>0</v>
       </c>
       <c r="K355" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L355" s="3" t="s">
         <v>10</v>
@@ -19215,15 +19212,15 @@
         <v>120</v>
       </c>
       <c r="N355" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A356" s="4" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C356" s="3" t="s">
         <v>44</v>
@@ -19251,7 +19248,7 @@
         <v>0</v>
       </c>
       <c r="K356" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L356" s="3" t="s">
         <v>10</v>
@@ -19260,15 +19257,15 @@
         <v>120</v>
       </c>
       <c r="N356" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A357" s="4" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C357" s="3" t="s">
         <v>44</v>
@@ -19290,13 +19287,13 @@
         <v>36</v>
       </c>
       <c r="I357" s="3" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="J357" s="5">
         <v>40</v>
       </c>
       <c r="K357" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L357" s="3" t="s">
         <v>10</v>
@@ -19305,15 +19302,15 @@
         <v>120</v>
       </c>
       <c r="N357" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A358" s="4" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C358" s="3" t="s">
         <v>44</v>
@@ -19341,7 +19338,7 @@
         <v>0</v>
       </c>
       <c r="K358" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L358" s="3" t="s">
         <v>10</v>
@@ -19350,15 +19347,15 @@
         <v>120</v>
       </c>
       <c r="N358" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="359" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A359" s="4" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C359" s="3" t="s">
         <v>44</v>
@@ -19386,7 +19383,7 @@
         <v>0</v>
       </c>
       <c r="K359" s="3" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="L359" s="3" t="s">
         <v>10</v>
@@ -19395,15 +19392,15 @@
         <v>120</v>
       </c>
       <c r="N359" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A360" s="4" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C360" s="3" t="s">
         <v>44</v>
@@ -19431,7 +19428,7 @@
         <v>0</v>
       </c>
       <c r="K360" s="3" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="L360" s="3" t="s">
         <v>10</v>
@@ -19440,15 +19437,15 @@
         <v>120</v>
       </c>
       <c r="N360" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="361" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A361" s="4" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C361" s="3" t="s">
         <v>44</v>
@@ -19476,7 +19473,7 @@
         <v>0</v>
       </c>
       <c r="K361" s="3" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="L361" s="3" t="s">
         <v>10</v>
@@ -19485,15 +19482,15 @@
         <v>120</v>
       </c>
       <c r="N361" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A362" s="4" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C362" s="3" t="s">
         <v>44</v>
@@ -19522,7 +19519,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="K362" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L362" s="3" t="s">
         <v>10</v>
@@ -19531,15 +19528,15 @@
         <v>120</v>
       </c>
       <c r="N362" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A363" s="4" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C363" s="3" t="s">
         <v>44</v>
@@ -19567,7 +19564,7 @@
         <v>0</v>
       </c>
       <c r="K363" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L363" s="3" t="s">
         <v>10</v>
@@ -19576,15 +19573,15 @@
         <v>120</v>
       </c>
       <c r="N363" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A364" s="4" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C364" s="3" t="s">
         <v>44</v>
@@ -19612,7 +19609,7 @@
         <v>0</v>
       </c>
       <c r="K364" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L364" s="3" t="s">
         <v>10</v>
@@ -19621,15 +19618,15 @@
         <v>120</v>
       </c>
       <c r="N364" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="365" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A365" s="4" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C365" s="3" t="s">
         <v>44</v>
@@ -19657,7 +19654,7 @@
         <v>0</v>
       </c>
       <c r="K365" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L365" s="3" t="s">
         <v>10</v>
@@ -19666,15 +19663,15 @@
         <v>120</v>
       </c>
       <c r="N365" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A366" s="4" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C366" s="3" t="s">
         <v>81</v>
@@ -19696,7 +19693,7 @@
         <v>54.5</v>
       </c>
       <c r="I366" s="3" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="J366" s="5">
         <f>6+0.5+2</f>
@@ -19709,18 +19706,18 @@
         <v>153</v>
       </c>
       <c r="M366" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="N366" s="7" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A367" s="4" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C367" s="3" t="s">
         <v>81</v>
@@ -19748,7 +19745,7 @@
         <v>0</v>
       </c>
       <c r="K367" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L367" s="3" t="s">
         <v>10</v>
@@ -19757,18 +19754,18 @@
         <v>21</v>
       </c>
       <c r="N367" s="7" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A368" s="4" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B368" s="23" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C368" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D368" s="5">
         <v>5.3038499999999997</v>
@@ -19802,15 +19799,15 @@
         <v>21</v>
       </c>
       <c r="N368" s="7" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="369" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A369" s="4" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C369" s="3" t="s">
         <v>58</v>
@@ -19832,7 +19829,7 @@
         <v>35</v>
       </c>
       <c r="I369" s="10" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="J369" s="5">
         <v>4</v>
@@ -19841,21 +19838,21 @@
         <v>221</v>
       </c>
       <c r="L369" s="3" t="s">
-        <v>522</v>
+        <v>753</v>
       </c>
       <c r="M369" s="3" t="s">
         <v>21</v>
       </c>
       <c r="N369" s="25" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A370" s="4" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C370" s="3" t="s">
         <v>58</v>
@@ -19877,13 +19874,13 @@
         <v>91</v>
       </c>
       <c r="I370" s="10" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="J370" s="5">
         <v>4</v>
       </c>
       <c r="K370" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L370" s="3" t="s">
         <v>10</v>
@@ -19892,15 +19889,15 @@
         <v>120</v>
       </c>
       <c r="N370" s="25" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="371" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A371" s="4" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B371" s="26" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C371" s="3" t="s">
         <v>19</v>
@@ -19932,21 +19929,21 @@
         <v>221</v>
       </c>
       <c r="L371" s="3" t="s">
-        <v>525</v>
+        <v>754</v>
       </c>
       <c r="M371" s="3" t="s">
         <v>21</v>
       </c>
       <c r="N371" s="6" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A372" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B372" s="27" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C372" s="3" t="s">
         <v>29</v>
@@ -19975,7 +19972,7 @@
         <v>31</v>
       </c>
       <c r="K372" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L372" s="3" t="s">
         <v>10</v>
@@ -19984,15 +19981,15 @@
         <v>120</v>
       </c>
       <c r="N372" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A373" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B373" s="27" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C373" s="3" t="s">
         <v>29</v>
@@ -20021,7 +20018,7 @@
         <v>2</v>
       </c>
       <c r="K373" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L373" s="3" t="s">
         <v>10</v>
@@ -20030,15 +20027,15 @@
         <v>120</v>
       </c>
       <c r="N373" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A374" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B374" s="27" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="C374" s="3" t="s">
         <v>29</v>
@@ -20067,7 +20064,7 @@
         <v>2.8999999999999986</v>
       </c>
       <c r="K374" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L374" s="3" t="s">
         <v>10</v>
@@ -20076,15 +20073,15 @@
         <v>120</v>
       </c>
       <c r="N374" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A375" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B375" s="27" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="C375" s="3" t="s">
         <v>29</v>
@@ -20113,7 +20110,7 @@
         <v>20.099999999999994</v>
       </c>
       <c r="K375" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L375" s="3" t="s">
         <v>10</v>
@@ -20122,15 +20119,15 @@
         <v>120</v>
       </c>
       <c r="N375" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="376" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A376" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B376" s="27" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="C376" s="3" t="s">
         <v>29</v>
@@ -20159,7 +20156,7 @@
         <v>1</v>
       </c>
       <c r="K376" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L376" s="3" t="s">
         <v>10</v>
@@ -20168,15 +20165,15 @@
         <v>120</v>
       </c>
       <c r="N376" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A377" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B377" s="27" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="C377" s="3" t="s">
         <v>29</v>
@@ -20205,7 +20202,7 @@
         <v>30.299999999999997</v>
       </c>
       <c r="K377" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L377" s="3" t="s">
         <v>10</v>
@@ -20214,15 +20211,15 @@
         <v>120</v>
       </c>
       <c r="N377" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A378" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B378" s="27" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="C378" s="3" t="s">
         <v>29</v>
@@ -20251,7 +20248,7 @@
         <v>16.799999999999997</v>
       </c>
       <c r="K378" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L378" s="3" t="s">
         <v>10</v>
@@ -20260,15 +20257,15 @@
         <v>120</v>
       </c>
       <c r="N378" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="379" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A379" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B379" s="27" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C379" s="3" t="s">
         <v>29</v>
@@ -20297,7 +20294,7 @@
         <v>14.100000000000001</v>
       </c>
       <c r="K379" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L379" s="3" t="s">
         <v>10</v>
@@ -20306,15 +20303,15 @@
         <v>120</v>
       </c>
       <c r="N379" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="380" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A380" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B380" s="26" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C380" s="3" t="s">
         <v>29</v>
@@ -20343,7 +20340,7 @@
         <v>43.2</v>
       </c>
       <c r="K380" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L380" s="3" t="s">
         <v>10</v>
@@ -20352,15 +20349,15 @@
         <v>120</v>
       </c>
       <c r="N380" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A381" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B381" s="26" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="C381" s="3" t="s">
         <v>29</v>
@@ -20389,7 +20386,7 @@
         <v>24.200000000000003</v>
       </c>
       <c r="K381" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L381" s="3" t="s">
         <v>10</v>
@@ -20398,15 +20395,15 @@
         <v>120</v>
       </c>
       <c r="N381" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="382" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A382" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B382" s="26" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C382" s="3" t="s">
         <v>29</v>
@@ -20435,7 +20432,7 @@
         <v>15.400000000000006</v>
       </c>
       <c r="K382" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L382" s="3" t="s">
         <v>10</v>
@@ -20444,15 +20441,15 @@
         <v>120</v>
       </c>
       <c r="N382" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="383" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A383" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B383" s="26" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C383" s="3" t="s">
         <v>29</v>
@@ -20481,7 +20478,7 @@
         <v>7.7000000000000028</v>
       </c>
       <c r="K383" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L383" s="3" t="s">
         <v>10</v>
@@ -20490,15 +20487,15 @@
         <v>120</v>
       </c>
       <c r="N383" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="384" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A384" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B384" s="26" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C384" s="3" t="s">
         <v>29</v>
@@ -20527,7 +20524,7 @@
         <v>13</v>
       </c>
       <c r="K384" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L384" s="3" t="s">
         <v>10</v>
@@ -20536,15 +20533,15 @@
         <v>120</v>
       </c>
       <c r="N384" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="385" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A385" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B385" s="30" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="C385" s="3" t="s">
         <v>29</v>
@@ -20573,7 +20570,7 @@
         <v>17.200000000000003</v>
       </c>
       <c r="K385" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L385" s="3" t="s">
         <v>10</v>
@@ -20582,15 +20579,15 @@
         <v>120</v>
       </c>
       <c r="N385" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="386" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A386" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B386" s="26" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="C386" s="3" t="s">
         <v>29</v>
@@ -20619,7 +20616,7 @@
         <v>7.7999999999999972</v>
       </c>
       <c r="K386" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L386" s="3" t="s">
         <v>10</v>
@@ -20628,15 +20625,15 @@
         <v>120</v>
       </c>
       <c r="N386" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="387" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A387" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B387" s="26" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="C387" s="3" t="s">
         <v>29</v>
@@ -20665,7 +20662,7 @@
         <v>14.400000000000006</v>
       </c>
       <c r="K387" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L387" s="3" t="s">
         <v>10</v>
@@ -20674,15 +20671,15 @@
         <v>120</v>
       </c>
       <c r="N387" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="388" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A388" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B388" s="26" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C388" s="3" t="s">
         <v>29</v>
@@ -20711,7 +20708,7 @@
         <v>23.5</v>
       </c>
       <c r="K388" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L388" s="3" t="s">
         <v>10</v>
@@ -20720,15 +20717,15 @@
         <v>120</v>
       </c>
       <c r="N388" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="389" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A389" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B389" s="26" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C389" s="3" t="s">
         <v>29</v>
@@ -20757,7 +20754,7 @@
         <v>4</v>
       </c>
       <c r="K389" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L389" s="3" t="s">
         <v>10</v>
@@ -20766,15 +20763,15 @@
         <v>120</v>
       </c>
       <c r="N389" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="390" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A390" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B390" s="26" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="C390" s="3" t="s">
         <v>29</v>
@@ -20803,7 +20800,7 @@
         <v>10.599999999999994</v>
       </c>
       <c r="K390" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L390" s="3" t="s">
         <v>10</v>
@@ -20812,15 +20809,15 @@
         <v>120</v>
       </c>
       <c r="N390" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="391" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A391" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B391" s="26" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C391" s="3" t="s">
         <v>29</v>
@@ -20849,7 +20846,7 @@
         <v>7</v>
       </c>
       <c r="K391" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L391" s="3" t="s">
         <v>10</v>
@@ -20858,15 +20855,15 @@
         <v>120</v>
       </c>
       <c r="N391" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="392" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A392" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B392" s="26" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C392" s="3" t="s">
         <v>29</v>
@@ -20895,7 +20892,7 @@
         <v>6</v>
       </c>
       <c r="K392" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L392" s="3" t="s">
         <v>10</v>
@@ -20904,15 +20901,15 @@
         <v>120</v>
       </c>
       <c r="N392" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="393" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A393" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B393" s="26" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C393" s="3" t="s">
         <v>29</v>
@@ -20940,7 +20937,7 @@
         <v>6</v>
       </c>
       <c r="K393" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L393" s="3" t="s">
         <v>10</v>
@@ -20949,15 +20946,15 @@
         <v>120</v>
       </c>
       <c r="N393" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="394" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A394" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B394" s="26" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C394" s="3" t="s">
         <v>29</v>
@@ -20986,7 +20983,7 @@
         <v>13.200000000000003</v>
       </c>
       <c r="K394" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L394" s="3" t="s">
         <v>10</v>
@@ -20995,15 +20992,15 @@
         <v>120</v>
       </c>
       <c r="N394" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="395" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A395" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B395" s="26" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="C395" s="3" t="s">
         <v>29</v>
@@ -21032,7 +21029,7 @@
         <v>5.5</v>
       </c>
       <c r="K395" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L395" s="3" t="s">
         <v>10</v>
@@ -21041,15 +21038,15 @@
         <v>120</v>
       </c>
       <c r="N395" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="396" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A396" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B396" s="26" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C396" s="3" t="s">
         <v>29</v>
@@ -21078,7 +21075,7 @@
         <v>58.2</v>
       </c>
       <c r="K396" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L396" s="3" t="s">
         <v>10</v>
@@ -21087,15 +21084,15 @@
         <v>120</v>
       </c>
       <c r="N396" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="397" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A397" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B397" s="31" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="C397" s="3" t="s">
         <v>29</v>
@@ -21122,7 +21119,7 @@
         <v>30</v>
       </c>
       <c r="K397" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L397" s="3" t="s">
         <v>10</v>
@@ -21131,15 +21128,15 @@
         <v>120</v>
       </c>
       <c r="N397" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="398" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A398" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B398" s="31" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C398" s="3" t="s">
         <v>29</v>
@@ -21166,7 +21163,7 @@
         <v>30</v>
       </c>
       <c r="K398" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L398" s="3" t="s">
         <v>10</v>
@@ -21175,15 +21172,15 @@
         <v>120</v>
       </c>
       <c r="N398" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="399" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A399" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B399" s="31" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C399" s="3" t="s">
         <v>29</v>
@@ -21210,7 +21207,7 @@
         <v>30</v>
       </c>
       <c r="K399" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L399" s="3" t="s">
         <v>10</v>
@@ -21219,15 +21216,15 @@
         <v>120</v>
       </c>
       <c r="N399" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="400" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A400" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B400" s="31" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C400" s="3" t="s">
         <v>29</v>
@@ -21254,7 +21251,7 @@
         <v>30</v>
       </c>
       <c r="K400" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L400" s="3" t="s">
         <v>10</v>
@@ -21263,15 +21260,15 @@
         <v>120</v>
       </c>
       <c r="N400" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="401" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A401" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B401" s="31" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C401" s="3" t="s">
         <v>29</v>
@@ -21298,7 +21295,7 @@
         <v>30</v>
       </c>
       <c r="K401" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L401" s="3" t="s">
         <v>10</v>
@@ -21307,15 +21304,15 @@
         <v>120</v>
       </c>
       <c r="N401" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="402" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A402" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B402" s="31" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C402" s="3" t="s">
         <v>29</v>
@@ -21342,7 +21339,7 @@
         <v>30</v>
       </c>
       <c r="K402" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L402" s="3" t="s">
         <v>10</v>
@@ -21351,15 +21348,15 @@
         <v>120</v>
       </c>
       <c r="N402" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="403" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A403" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B403" s="31" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C403" s="3" t="s">
         <v>29</v>
@@ -21386,7 +21383,7 @@
         <v>30</v>
       </c>
       <c r="K403" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L403" s="3" t="s">
         <v>10</v>
@@ -21395,15 +21392,15 @@
         <v>120</v>
       </c>
       <c r="N403" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="404" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A404" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B404" s="31" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C404" s="3" t="s">
         <v>29</v>
@@ -21430,7 +21427,7 @@
         <v>30</v>
       </c>
       <c r="K404" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L404" s="3" t="s">
         <v>10</v>
@@ -21439,15 +21436,15 @@
         <v>120</v>
       </c>
       <c r="N404" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="405" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A405" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B405" s="31" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C405" s="3" t="s">
         <v>29</v>
@@ -21474,7 +21471,7 @@
         <v>30</v>
       </c>
       <c r="K405" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L405" s="3" t="s">
         <v>10</v>
@@ -21483,15 +21480,15 @@
         <v>120</v>
       </c>
       <c r="N405" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="406" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A406" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B406" s="31" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C406" s="3" t="s">
         <v>29</v>
@@ -21518,7 +21515,7 @@
         <v>30</v>
       </c>
       <c r="K406" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L406" s="3" t="s">
         <v>10</v>
@@ -21527,15 +21524,15 @@
         <v>120</v>
       </c>
       <c r="N406" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="407" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A407" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B407" s="31" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C407" s="3" t="s">
         <v>29</v>
@@ -21562,7 +21559,7 @@
         <v>30</v>
       </c>
       <c r="K407" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L407" s="3" t="s">
         <v>10</v>
@@ -21571,15 +21568,15 @@
         <v>120</v>
       </c>
       <c r="N407" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="408" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A408" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B408" s="31" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C408" s="3" t="s">
         <v>29</v>
@@ -21606,7 +21603,7 @@
         <v>30</v>
       </c>
       <c r="K408" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L408" s="3" t="s">
         <v>10</v>
@@ -21615,15 +21612,15 @@
         <v>120</v>
       </c>
       <c r="N408" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="409" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A409" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B409" s="31" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="C409" s="3" t="s">
         <v>29</v>
@@ -21650,7 +21647,7 @@
         <v>30</v>
       </c>
       <c r="K409" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L409" s="3" t="s">
         <v>10</v>
@@ -21659,15 +21656,15 @@
         <v>120</v>
       </c>
       <c r="N409" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="410" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A410" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B410" s="31" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="C410" s="3" t="s">
         <v>29</v>
@@ -21694,7 +21691,7 @@
         <v>30</v>
       </c>
       <c r="K410" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L410" s="3" t="s">
         <v>10</v>
@@ -21703,15 +21700,15 @@
         <v>120</v>
       </c>
       <c r="N410" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="411" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A411" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B411" s="31" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="C411" s="3" t="s">
         <v>29</v>
@@ -21738,7 +21735,7 @@
         <v>30</v>
       </c>
       <c r="K411" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L411" s="3" t="s">
         <v>10</v>
@@ -21747,15 +21744,15 @@
         <v>120</v>
       </c>
       <c r="N411" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="412" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A412" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B412" s="31" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C412" s="3" t="s">
         <v>29</v>
@@ -21782,7 +21779,7 @@
         <v>30</v>
       </c>
       <c r="K412" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L412" s="3" t="s">
         <v>10</v>
@@ -21791,15 +21788,15 @@
         <v>120</v>
       </c>
       <c r="N412" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="413" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A413" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B413" s="31" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C413" s="3" t="s">
         <v>29</v>
@@ -21826,7 +21823,7 @@
         <v>30</v>
       </c>
       <c r="K413" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L413" s="3" t="s">
         <v>10</v>
@@ -21835,15 +21832,15 @@
         <v>120</v>
       </c>
       <c r="N413" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="414" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A414" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B414" s="31" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="C414" s="3" t="s">
         <v>29</v>
@@ -21870,7 +21867,7 @@
         <v>30</v>
       </c>
       <c r="K414" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L414" s="3" t="s">
         <v>10</v>
@@ -21879,15 +21876,15 @@
         <v>120</v>
       </c>
       <c r="N414" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="415" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A415" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B415" s="31" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C415" s="3" t="s">
         <v>29</v>
@@ -21914,7 +21911,7 @@
         <v>30</v>
       </c>
       <c r="K415" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L415" s="3" t="s">
         <v>10</v>
@@ -21923,15 +21920,15 @@
         <v>120</v>
       </c>
       <c r="N415" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="416" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A416" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B416" s="31" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C416" s="3" t="s">
         <v>29</v>
@@ -21958,7 +21955,7 @@
         <v>30</v>
       </c>
       <c r="K416" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L416" s="3" t="s">
         <v>10</v>
@@ -21967,15 +21964,15 @@
         <v>120</v>
       </c>
       <c r="N416" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="417" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A417" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B417" s="31" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="C417" s="3" t="s">
         <v>29</v>
@@ -22002,7 +21999,7 @@
         <v>30</v>
       </c>
       <c r="K417" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L417" s="3" t="s">
         <v>10</v>
@@ -22011,15 +22008,15 @@
         <v>120</v>
       </c>
       <c r="N417" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="418" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A418" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B418" s="31" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="C418" s="3" t="s">
         <v>29</v>
@@ -22046,7 +22043,7 @@
         <v>30</v>
       </c>
       <c r="K418" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L418" s="3" t="s">
         <v>10</v>
@@ -22055,15 +22052,15 @@
         <v>120</v>
       </c>
       <c r="N418" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="419" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A419" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B419" s="31" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C419" s="3" t="s">
         <v>29</v>
@@ -22090,7 +22087,7 @@
         <v>30</v>
       </c>
       <c r="K419" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L419" s="3" t="s">
         <v>10</v>
@@ -22099,15 +22096,15 @@
         <v>120</v>
       </c>
       <c r="N419" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="420" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A420" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B420" s="31" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C420" s="3" t="s">
         <v>29</v>
@@ -22134,7 +22131,7 @@
         <v>30</v>
       </c>
       <c r="K420" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L420" s="3" t="s">
         <v>10</v>
@@ -22143,15 +22140,15 @@
         <v>120</v>
       </c>
       <c r="N420" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="421" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A421" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B421" s="31" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C421" s="3" t="s">
         <v>29</v>
@@ -22178,7 +22175,7 @@
         <v>30</v>
       </c>
       <c r="K421" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L421" s="3" t="s">
         <v>10</v>
@@ -22187,15 +22184,15 @@
         <v>120</v>
       </c>
       <c r="N421" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="422" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A422" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B422" s="31" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C422" s="3" t="s">
         <v>29</v>
@@ -22222,7 +22219,7 @@
         <v>30</v>
       </c>
       <c r="K422" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L422" s="3" t="s">
         <v>10</v>
@@ -22231,15 +22228,15 @@
         <v>120</v>
       </c>
       <c r="N422" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="423" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A423" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B423" s="31" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C423" s="3" t="s">
         <v>29</v>
@@ -22266,7 +22263,7 @@
         <v>30</v>
       </c>
       <c r="K423" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L423" s="3" t="s">
         <v>10</v>
@@ -22275,15 +22272,15 @@
         <v>120</v>
       </c>
       <c r="N423" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="424" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A424" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B424" s="31" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C424" s="3" t="s">
         <v>29</v>
@@ -22310,7 +22307,7 @@
         <v>30</v>
       </c>
       <c r="K424" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L424" s="3" t="s">
         <v>10</v>
@@ -22319,15 +22316,15 @@
         <v>120</v>
       </c>
       <c r="N424" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="425" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A425" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B425" s="31" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C425" s="3" t="s">
         <v>29</v>
@@ -22354,7 +22351,7 @@
         <v>30</v>
       </c>
       <c r="K425" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L425" s="3" t="s">
         <v>10</v>
@@ -22363,15 +22360,15 @@
         <v>120</v>
       </c>
       <c r="N425" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="426" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A426" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B426" s="31" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C426" s="3" t="s">
         <v>29</v>
@@ -22398,7 +22395,7 @@
         <v>30</v>
       </c>
       <c r="K426" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L426" s="3" t="s">
         <v>10</v>
@@ -22407,15 +22404,15 @@
         <v>120</v>
       </c>
       <c r="N426" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="427" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A427" s="4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B427" s="31" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C427" s="3" t="s">
         <v>29</v>
@@ -22442,7 +22439,7 @@
         <v>30</v>
       </c>
       <c r="K427" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L427" s="3" t="s">
         <v>10</v>
@@ -22451,15 +22448,15 @@
         <v>120</v>
       </c>
       <c r="N427" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="428" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A428" s="4" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C428" s="3" t="s">
         <v>44</v>
@@ -22487,24 +22484,24 @@
         <v>0</v>
       </c>
       <c r="K428" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L428" s="3" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="M428" s="3" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="N428" s="6" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
     </row>
     <row r="429" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A429" s="4" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C429" s="3" t="s">
         <v>44</v>
@@ -22532,27 +22529,27 @@
         <v>0</v>
       </c>
       <c r="K429" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L429" s="3" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="M429" s="3" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="N429" s="6" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
     </row>
     <row r="430" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A430" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C430" s="3" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D430" s="5">
         <v>1.2865660000000001</v>
@@ -22571,13 +22568,13 @@
         <v>1.5</v>
       </c>
       <c r="I430" s="3" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="J430" s="5">
         <v>6.5</v>
       </c>
       <c r="K430" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L430" s="3" t="s">
         <v>30</v>
@@ -22586,18 +22583,18 @@
         <v>120</v>
       </c>
       <c r="N430" s="6" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
     </row>
     <row r="431" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A431" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C431" s="3" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D431" s="5">
         <v>1.2865660000000001</v>
@@ -22616,13 +22613,13 @@
         <v>1</v>
       </c>
       <c r="I431" s="3" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="J431" s="5">
         <v>1</v>
       </c>
       <c r="K431" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L431" s="3" t="s">
         <v>30</v>
@@ -22631,18 +22628,18 @@
         <v>31</v>
       </c>
       <c r="N431" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="432" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A432" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C432" s="3" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D432" s="8">
         <v>1.2669999999999999</v>
@@ -22661,13 +22658,13 @@
         <v>1</v>
       </c>
       <c r="I432" s="3" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="J432" s="5">
         <v>0</v>
       </c>
       <c r="K432" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L432" s="3" t="s">
         <v>30</v>
@@ -22676,18 +22673,18 @@
         <v>120</v>
       </c>
       <c r="N432" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="433" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A433" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C433" s="3" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D433" s="8">
         <v>1.2669999999999999</v>
@@ -22712,7 +22709,7 @@
         <v>0</v>
       </c>
       <c r="K433" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L433" s="3" t="s">
         <v>30</v>
@@ -22721,18 +22718,18 @@
         <v>31</v>
       </c>
       <c r="N433" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="434" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A434" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C434" s="3" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D434" s="8">
         <v>1.2669999999999999</v>
@@ -22751,33 +22748,33 @@
         <v>5.09</v>
       </c>
       <c r="I434" s="3" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="J434" s="5">
         <v>0.91</v>
       </c>
       <c r="K434" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L434" s="3" t="s">
         <v>30</v>
       </c>
       <c r="M434" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="N434" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="435" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A435" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="C435" s="3" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D435" s="8">
         <v>1.462</v>
@@ -22796,13 +22793,13 @@
         <v>2.33</v>
       </c>
       <c r="I435" s="3" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="J435" s="3">
         <v>4.67</v>
       </c>
       <c r="K435" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L435" s="3" t="s">
         <v>30</v>
@@ -22811,18 +22808,18 @@
         <v>236</v>
       </c>
       <c r="N435" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="436" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A436" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C436" s="3" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D436" s="8">
         <v>1.4670000000000001</v>
@@ -22841,7 +22838,7 @@
         <v>8.9999999999999969E-2</v>
       </c>
       <c r="I436" s="3" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="J436" s="5">
         <v>0.91</v>
@@ -22856,18 +22853,18 @@
         <v>21</v>
       </c>
       <c r="N436" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="437" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A437" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="C437" s="3" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="D437" s="8">
         <v>-22.954810999999999</v>
@@ -22886,7 +22883,7 @@
         <v>35</v>
       </c>
       <c r="I437" s="3" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="J437" s="5">
         <v>22</v>
@@ -22901,18 +22898,18 @@
         <v>236</v>
       </c>
       <c r="N437" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="438" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A438" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="C438" s="3" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D438" s="8">
         <v>-26.643184000000002</v>
@@ -22931,7 +22928,7 @@
         <v>44</v>
       </c>
       <c r="I438" s="3" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="J438" s="5">
         <v>13</v>
@@ -22946,18 +22943,18 @@
         <v>236</v>
       </c>
       <c r="N438" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="439" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A439" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C439" s="3" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D439" s="8">
         <v>-29.265045000000001</v>
@@ -22976,7 +22973,7 @@
         <v>53</v>
       </c>
       <c r="I439" s="3" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="J439" s="5">
         <v>6</v>
@@ -22991,18 +22988,18 @@
         <v>236</v>
       </c>
       <c r="N439" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="440" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A440" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="C440" s="3" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D440" s="8">
         <v>-32.723230999999998</v>
@@ -23036,18 +23033,18 @@
         <v>236</v>
       </c>
       <c r="N440" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="441" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A441" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C441" s="3" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D441" s="8">
         <v>-33.003106000000002</v>
@@ -23066,7 +23063,7 @@
         <v>35</v>
       </c>
       <c r="I441" s="3" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="J441" s="5">
         <v>10</v>
@@ -23081,18 +23078,18 @@
         <v>236</v>
       </c>
       <c r="N441" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="442" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A442" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C442" s="3" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D442" s="8">
         <v>-33.797657000000001</v>
@@ -23126,18 +23123,18 @@
         <v>236</v>
       </c>
       <c r="N442" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="443" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A443" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C443" s="3" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D443" s="8">
         <v>-33.901017000000003</v>
@@ -23156,7 +23153,7 @@
         <v>42</v>
       </c>
       <c r="I443" s="3" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="J443" s="5">
         <v>9</v>
@@ -23171,18 +23168,18 @@
         <v>236</v>
       </c>
       <c r="N443" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="444" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A444" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C444" s="3" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D444" s="8">
         <v>-33.906410999999999</v>
@@ -23201,7 +23198,7 @@
         <v>31</v>
       </c>
       <c r="I444" s="3" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J444" s="5">
         <v>52</v>
@@ -23216,18 +23213,18 @@
         <v>236</v>
       </c>
       <c r="N444" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="445" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A445" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="C445" s="3" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D445" s="8">
         <v>-34.051886000000003</v>
@@ -23246,7 +23243,7 @@
         <v>9</v>
       </c>
       <c r="I445" s="3" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="J445" s="5">
         <v>10</v>
@@ -23261,18 +23258,18 @@
         <v>236</v>
       </c>
       <c r="N445" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="446" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A446" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C446" s="3" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D446" s="8">
         <v>-34.189658000000001</v>
@@ -23291,7 +23288,7 @@
         <v>53</v>
       </c>
       <c r="I446" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="J446" s="5">
         <v>133</v>
@@ -23306,18 +23303,18 @@
         <v>236</v>
       </c>
       <c r="N446" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="447" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A447" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C447" s="3" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D447" s="8">
         <v>-34.434364000000002</v>
@@ -23351,18 +23348,18 @@
         <v>236</v>
       </c>
       <c r="N447" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="448" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A448" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C448" s="3" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D448" s="8">
         <v>-34.178418000000001</v>
@@ -23381,7 +23378,7 @@
         <v>48</v>
       </c>
       <c r="I448" s="3" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="J448" s="5">
         <v>11</v>
@@ -23396,18 +23393,18 @@
         <v>236</v>
       </c>
       <c r="N448" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="449" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A449" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="C449" s="3" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D449" s="8">
         <v>-34.041114999999998</v>
@@ -23426,7 +23423,7 @@
         <v>38</v>
       </c>
       <c r="I449" s="3" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="J449" s="5">
         <v>19</v>
@@ -23441,18 +23438,18 @@
         <v>236</v>
       </c>
       <c r="N449" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="450" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A450" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C450" s="3" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D450" s="8">
         <v>-33.961784999999999</v>
@@ -23471,7 +23468,7 @@
         <v>43</v>
       </c>
       <c r="I450" s="3" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="J450" s="5">
         <v>82</v>
@@ -23486,18 +23483,18 @@
         <v>236</v>
       </c>
       <c r="N450" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="451" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A451" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C451" s="3" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D451" s="8">
         <v>-33.025978000000002</v>
@@ -23516,7 +23513,7 @@
         <v>36</v>
       </c>
       <c r="I451" s="3" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="J451" s="5">
         <v>16</v>
@@ -23531,18 +23528,18 @@
         <v>236</v>
       </c>
       <c r="N451" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="452" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A452" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C452" s="3" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D452" s="8">
         <v>-29.873816000000001</v>
@@ -23561,7 +23558,7 @@
         <v>52</v>
       </c>
       <c r="I452" s="3" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="J452" s="5">
         <v>87</v>
@@ -23576,18 +23573,18 @@
         <v>236</v>
       </c>
       <c r="N452" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="453" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A453" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="C453" s="3" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D453" s="8">
         <v>-28.794550999999998</v>
@@ -23606,7 +23603,7 @@
         <v>24</v>
       </c>
       <c r="I453" s="3" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="J453" s="5">
         <v>17</v>
@@ -23621,15 +23618,15 @@
         <v>236</v>
       </c>
       <c r="N453" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="454" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A454" s="4" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="C454" s="3" t="s">
         <v>44</v>
@@ -23651,7 +23648,7 @@
         <v>1.5769230769230802</v>
       </c>
       <c r="I454" s="3" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="J454" s="5">
         <v>80.42307692307692</v>
@@ -23663,18 +23660,18 @@
         <v>10</v>
       </c>
       <c r="M454" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="N454" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="455" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A455" s="4" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C455" s="3" t="s">
         <v>44</v>
@@ -23696,7 +23693,7 @@
         <v>1.25</v>
       </c>
       <c r="I455" s="3" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="J455" s="5">
         <v>63.75</v>
@@ -23708,18 +23705,18 @@
         <v>10</v>
       </c>
       <c r="M455" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="N455" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="456" spans="1:23" s="33" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A456" s="4" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="B456" s="33" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C456" s="33" t="s">
         <v>44</v>
@@ -23741,7 +23738,7 @@
         <v>1.2115384615384599</v>
       </c>
       <c r="I456" s="33" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="J456" s="34">
         <v>61.78846153846154</v>
@@ -23753,10 +23750,10 @@
         <v>10</v>
       </c>
       <c r="M456" s="33" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="N456" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="O456"/>
       <c r="P456"/>
@@ -23769,10 +23766,10 @@
     </row>
     <row r="457" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A457" s="4" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="C457" s="3" t="s">
         <v>44</v>
@@ -23794,7 +23791,7 @@
         <v>0.8461538461538467</v>
       </c>
       <c r="I457" s="3" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="J457" s="5">
         <v>43.153846153846153</v>
@@ -23806,10 +23803,10 @@
         <v>10</v>
       </c>
       <c r="M457" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="N457" s="41" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="W457" s="40"/>
     </row>
